--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127301890</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97314</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Backagruvan, Västmanland, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>482883</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6631269</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127072854</v>
+        <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>97320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemmanet, Hemmanet, Vstm</t>
+          <t>Backagruvan, Västmanland, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482830</v>
+        <v>482883</v>
       </c>
       <c r="R2" t="n">
-        <v>6631319</v>
+        <v>6631269</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +747,9 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127301890</v>
+        <v>127072854</v>
       </c>
       <c r="B3" t="n">
-        <v>97314</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,41 +788,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backagruvan, Västmanland, Vstm</t>
+          <t>Hemmanet, Hemmanet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482883</v>
+        <v>482830</v>
       </c>
       <c r="R3" t="n">
-        <v>6631269</v>
+        <v>6631319</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,9 +850,19 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,19 +871,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127072854</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127072854</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127072854</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127072854</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127301890</v>
+        <v>127072854</v>
       </c>
       <c r="B2" t="n">
-        <v>97346</v>
+        <v>58027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backagruvan, Västmanland, Vstm</t>
+          <t>Hemmanet, Hemmanet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482883</v>
+        <v>482830</v>
       </c>
       <c r="R2" t="n">
-        <v>6631269</v>
+        <v>6631319</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,9 +748,19 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,29 +769,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127072854</v>
+        <v>127301890</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>97314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,42 +803,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hemmanet, Hemmanet, Vstm</t>
+          <t>Backagruvan, Västmanland, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482830</v>
+        <v>482883</v>
       </c>
       <c r="R3" t="n">
-        <v>6631319</v>
+        <v>6631269</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +864,9 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,23 +875,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127072854</v>
+        <v>127301890</v>
       </c>
       <c r="B2" t="n">
-        <v>58027</v>
+        <v>97346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemmanet, Hemmanet, Vstm</t>
+          <t>Backagruvan, Västmanland, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482830</v>
+        <v>482883</v>
       </c>
       <c r="R2" t="n">
-        <v>6631319</v>
+        <v>6631269</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +747,9 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Anna Hammar</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127301890</v>
+        <v>127072854</v>
       </c>
       <c r="B3" t="n">
-        <v>97314</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,41 +788,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backagruvan, Västmanland, Vstm</t>
+          <t>Hemmanet, Hemmanet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482883</v>
+        <v>482830</v>
       </c>
       <c r="R3" t="n">
-        <v>6631269</v>
+        <v>6631319</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,9 +850,19 @@
           <t>2025-08-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,19 +871,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127301890</v>
+        <v>104518408</v>
       </c>
       <c r="B2" t="n">
-        <v>97346</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backagruvan, Västmanland, Vstm</t>
+          <t>Jönshyttan, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482883</v>
+        <v>482767</v>
       </c>
       <c r="R2" t="n">
-        <v>6631269</v>
+        <v>6631386</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2022-10-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Hammar</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,7 +775,7 @@
         <v>127072854</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,6 +886,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127301890</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backagruvan, Västmanland, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>482883</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6631269</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjulsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna Hammar</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16932-2025 artfynd.xlsx
+++ b/artfynd/A 16932-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127072854</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127301890</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>